--- a/data/trans_orig/P33B3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023</t>
+          <t>Poblacion según la frecuencia con la que se despierta demasiado temprano de forma involuntaria en 2023 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>29337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53459</t>
+          <t>54157</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22617</t>
+          <t>21806</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38895</t>
+          <t>39494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56330</t>
+          <t>55874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86211</t>
+          <t>85844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23885</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44443</t>
+          <t>45298</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>46964</t>
+          <t>48171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57319</t>
+          <t>57282</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86668</t>
+          <t>86307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70512</t>
+          <t>70922</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105387</t>
+          <t>106291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>77732</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107131</t>
+          <t>107505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>157673</t>
+          <t>158213</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>199950</t>
+          <t>202007</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>325605</t>
+          <t>322744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>367881</t>
+          <t>365400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>270198</t>
+          <t>268958</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304201</t>
+          <t>303103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>67,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>609696</t>
+          <t>605884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>665584</t>
+          <t>660188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,3%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>40675</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22340</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39324</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>47403</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73131</t>
+          <t>74440</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20120</t>
+          <t>19924</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42648</t>
+          <t>40955</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>21467</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39043</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45856</t>
+          <t>46512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75202</t>
+          <t>75269</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69381</t>
+          <t>68339</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>102304</t>
+          <t>101724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71104</t>
+          <t>69278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96781</t>
+          <t>96506</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148744</t>
+          <t>148399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188447</t>
+          <t>190660</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,87%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>286675</t>
+          <t>285468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>327561</t>
+          <t>327478</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224532</t>
+          <t>224905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>255767</t>
+          <t>257177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>523571</t>
+          <t>519761</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>572829</t>
+          <t>571463</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15980</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>77168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16424</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29449</t>
+          <t>28760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28369</t>
+          <t>29794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99847</t>
+          <t>99435</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12614</t>
+          <t>15094</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73160</t>
+          <t>74333</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18949</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>35254</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27515</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102550</t>
+          <t>99926</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28168</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129465</t>
+          <t>131249</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24321</t>
+          <t>23631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39415</t>
+          <t>39430</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>44465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>160800</t>
+          <t>161831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397884</t>
+          <t>394896</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>610765</t>
+          <t>599194</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77996</t>
+          <t>78209</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98073</t>
+          <t>98640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>481466</t>
+          <t>482691</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>735268</t>
+          <t>723361</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>78832</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>114848</t>
+          <t>115189</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35311</t>
+          <t>40485</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>102612</t>
+          <t>99013</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123392</t>
+          <t>112021</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>202073</t>
+          <t>199547</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61895</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>95449</t>
+          <t>93944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42404</t>
+          <t>46518</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111271</t>
+          <t>111763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110291</t>
+          <t>108468</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>188462</t>
+          <t>189069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>154263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>203509</t>
+          <t>202392</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>73545</t>
+          <t>84229</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>193630</t>
+          <t>194888</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>240850</t>
+          <t>224325</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>375279</t>
+          <t>371238</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>651448</t>
+          <t>651722</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>719766</t>
+          <t>714485</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>582235</t>
+          <t>583929</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>824653</t>
+          <t>795699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>81,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1268016</t>
+          <t>1269862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1540651</t>
+          <t>1556235</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>77,31%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30024</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52457</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>78374</t>
+          <t>77971</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>127407</t>
+          <t>128772</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>116129</t>
+          <t>118012</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170735</t>
+          <t>170652</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32567</t>
+          <t>31295</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>58276</t>
+          <t>60211</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>87322</t>
+          <t>85584</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>134306</t>
+          <t>136951</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>128461</t>
+          <t>124622</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>179550</t>
+          <t>181225</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60138</t>
+          <t>60050</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>93484</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>113781</t>
+          <t>123210</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>184981</t>
+          <t>186450</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189950</t>
+          <t>188068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>262965</t>
+          <t>261550</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>292271</t>
+          <t>291949</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>335779</t>
+          <t>335644</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>410542</t>
+          <t>405175</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>571766</t>
+          <t>552265</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>728252</t>
+          <t>729541</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>871518</t>
+          <t>883500</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>67,29%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>72471</t>
+          <t>73614</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>99168</t>
+          <t>100261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>82920</t>
+          <t>81554</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>118870</t>
+          <t>116940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>71960</t>
+          <t>72016</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>98779</t>
+          <t>100211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73974</t>
+          <t>73134</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101441</t>
+          <t>102614</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11308</t>
+          <t>12608</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>40919</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>140334</t>
+          <t>138231</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>175528</t>
+          <t>175065</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>158821</t>
+          <t>157190</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>204144</t>
+          <t>202407</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>181454</t>
+          <t>181498</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>217716</t>
+          <t>216732</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>409656</t>
+          <t>412043</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>457726</t>
+          <t>460311</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>606061</t>
+          <t>606196</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>668513</t>
+          <t>669128</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,49%</t>
+          <t>60,51%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,79%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>207799</t>
+          <t>205327</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>296971</t>
+          <t>300903</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>281805</t>
+          <t>279847</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>387358</t>
+          <t>383159</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>519718</t>
+          <t>521949</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>663179</t>
+          <t>664264</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>172521</t>
+          <t>179940</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>261023</t>
+          <t>259750</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>308135</t>
+          <t>303126</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>416583</t>
+          <t>411233</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>514482</t>
+          <t>512049</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>659939</t>
+          <t>659755</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>410543</t>
+          <t>417499</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>582300</t>
+          <t>583326</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>546372</t>
+          <t>528572</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>731081</t>
+          <t>724153</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1025934</t>
+          <t>1016948</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1291148</t>
+          <t>1291411</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2263589</t>
+          <t>2263645</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2589380</t>
+          <t>2548960</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2067401</t>
+          <t>2078900</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2451463</t>
+          <t>2507773</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4379037</t>
+          <t>4374850</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4874395</t>
+          <t>4923105</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B3_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B3_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>39641</t>
+          <t>44317</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29337</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>59611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>33550</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21806</t>
+          <t>26109</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39494</t>
+          <t>45527</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>69543</t>
+          <t>77867</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55874</t>
+          <t>63305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85844</t>
+          <t>96546</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32447</t>
+          <t>35235</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>25063</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>47467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>42938</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>33270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48171</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>70561</t>
+          <t>78173</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>63495</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86307</t>
+          <t>94935</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86008</t>
+          <t>91849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70922</t>
+          <t>75165</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>106291</t>
+          <t>112116</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>92112</t>
+          <t>104461</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79143</t>
+          <t>88884</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>107505</t>
+          <t>121430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,22 +1021,22 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>178120</t>
+          <t>196310</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158213</t>
+          <t>172594</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>202007</t>
+          <t>220793</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,25%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>347116</t>
+          <t>379216</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>322744</t>
+          <t>356333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>365400</t>
+          <t>401012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>287340</t>
+          <t>307462</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>268958</t>
+          <t>290274</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>303103</t>
+          <t>325965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>634455</t>
+          <t>686679</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>605884</t>
+          <t>656415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>660188</t>
+          <t>714588</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,3%</t>
+          <t>68,77%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29725</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>45187</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29969</t>
+          <t>34439</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22683</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39071</t>
+          <t>44710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>59694</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48025</t>
+          <t>52722</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>74440</t>
+          <t>81141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29398</t>
+          <t>30058</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19943</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40955</t>
+          <t>41290</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>34090</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21467</t>
+          <t>25188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>44558</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>58426</t>
+          <t>64148</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>46512</t>
+          <t>50268</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75269</t>
+          <t>78941</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84757</t>
+          <t>91894</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>76098</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101724</t>
+          <t>111584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82976</t>
+          <t>90899</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69278</t>
+          <t>76177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>96506</t>
+          <t>106203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>167733</t>
+          <t>182793</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>148399</t>
+          <t>159726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190660</t>
+          <t>205567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>307365</t>
+          <t>328256</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>285468</t>
+          <t>308966</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>327478</t>
+          <t>351067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>240607</t>
+          <t>263715</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>224905</t>
+          <t>246725</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>257177</t>
+          <t>280521</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>547972</t>
+          <t>591971</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519761</t>
+          <t>564028</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>571463</t>
+          <t>618118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>451244</t>
+          <t>482224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>833824</t>
+          <t>905367</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44737</t>
+          <t>48971</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>37413</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>77168</t>
+          <t>61386</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16053</t>
+          <t>18442</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>66534</t>
+          <t>73743</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29794</t>
+          <t>60862</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>99435</t>
+          <t>89317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>13,55%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43288</t>
+          <t>45584</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>33632</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74333</t>
+          <t>59546</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>28415</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18949</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35254</t>
+          <t>38643</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>73999</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>59945</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>99926</t>
+          <t>91350</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>78295</t>
+          <t>85537</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>70962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131249</t>
+          <t>102986</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>33970</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>23631</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39430</t>
+          <t>42631</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>109645</t>
+          <t>119508</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>44465</t>
+          <t>102131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161831</t>
+          <t>138874</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>501944</t>
+          <t>291519</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>394896</t>
+          <t>268427</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>599194</t>
+          <t>312924</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>61,81%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>88405</t>
+          <t>100340</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78209</t>
+          <t>89435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98640</t>
+          <t>112305</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>590349</t>
+          <t>391859</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>482691</t>
+          <t>367904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>723361</t>
+          <t>415491</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>57,8%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>63,04%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>95482</t>
+          <t>106243</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>78832</t>
+          <t>88944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115189</t>
+          <t>128682</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>74238</t>
+          <t>86176</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40485</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99013</t>
+          <t>101758</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>169720</t>
+          <t>192419</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112021</t>
+          <t>168591</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>199547</t>
+          <t>214278</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>76551</t>
+          <t>84776</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>69168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93944</t>
+          <t>104819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>83268</t>
+          <t>90058</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46518</t>
+          <t>76694</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>106881</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>159819</t>
+          <t>174834</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>108468</t>
+          <t>153833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>189069</t>
+          <t>200683</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>178001</t>
+          <t>200004</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>154263</t>
+          <t>175850</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>202392</t>
+          <t>228512</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>146948</t>
+          <t>166134</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84229</t>
+          <t>148932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>194888</t>
+          <t>186743</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>324949</t>
+          <t>366138</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>224325</t>
+          <t>333459</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>371238</t>
+          <t>397930</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>684785</t>
+          <t>740820</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>651722</t>
+          <t>708950</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>714485</t>
+          <t>774347</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>673641</t>
+          <t>518843</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>583929</t>
+          <t>493090</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>795699</t>
+          <t>542600</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>60,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1358425</t>
+          <t>1259662</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1269862</t>
+          <t>1219730</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1556235</t>
+          <t>1301675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>65,31%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>978094</t>
+          <t>861211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012912</t>
+          <t>1993054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>43210</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>32767</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>56539</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>105338</t>
+          <t>117368</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77971</t>
+          <t>100979</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>128772</t>
+          <t>132903</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>145557</t>
+          <t>160578</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>118012</t>
+          <t>141048</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>170652</t>
+          <t>181364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>43667</t>
+          <t>47232</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31295</t>
+          <t>35039</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60211</t>
+          <t>66704</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>113601</t>
+          <t>123432</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85584</t>
+          <t>108308</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>136951</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>157268</t>
+          <t>170664</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124622</t>
+          <t>149475</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181225</t>
+          <t>194754</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>74646</t>
+          <t>83292</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>65791</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>92885</t>
+          <t>100875</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>158627</t>
+          <t>173979</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>123210</t>
+          <t>156270</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186450</t>
+          <t>193067</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>233273</t>
+          <t>257271</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>188068</t>
+          <t>230523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>261550</t>
+          <t>282910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>20,25%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>315483</t>
+          <t>393147</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>291949</t>
+          <t>369105</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>335644</t>
+          <t>417508</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>69,35%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>461431</t>
+          <t>415348</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>405175</t>
+          <t>393408</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>552265</t>
+          <t>440538</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>776913</t>
+          <t>808496</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>729541</t>
+          <t>773961</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>883500</t>
+          <t>843922</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>57,87%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>60,41%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1313012</t>
+          <t>1397009</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3400</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>27096</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>86383</t>
+          <t>96728</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>73614</t>
+          <t>82404</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>100261</t>
+          <t>111986</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>97954</t>
+          <t>107451</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>81554</t>
+          <t>90354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>116940</t>
+          <t>127679</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>84352</t>
+          <t>95198</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>72016</t>
+          <t>81275</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>100211</t>
+          <t>112766</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>87202</t>
+          <t>99403</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73134</t>
+          <t>83130</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>116951</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>22777</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12608</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40919</t>
+          <t>38514</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>156444</t>
+          <t>166787</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>138231</t>
+          <t>149010</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>175065</t>
+          <t>186755</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>179221</t>
+          <t>189845</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>157190</t>
+          <t>168866</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>202407</t>
+          <t>217836</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,14%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>203308</t>
+          <t>199241</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>181498</t>
+          <t>178901</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>216732</t>
+          <t>212870</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>434192</t>
+          <t>485569</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>412043</t>
+          <t>460140</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>460311</t>
+          <t>510957</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>637500</t>
+          <t>684810</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>606196</t>
+          <t>649027</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>669128</t>
+          <t>715797</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>63,63%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>261376</t>
+          <t>285481</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>205327</t>
+          <t>253323</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>300903</t>
+          <t>319845</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>347626</t>
+          <t>393033</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>279847</t>
+          <t>363655</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>383159</t>
+          <t>424349</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>609002</t>
+          <t>678514</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>521949</t>
+          <t>638160</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>664264</t>
+          <t>722671</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>228202</t>
+          <t>247092</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>179940</t>
+          <t>218584</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>259750</t>
+          <t>282404</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>373721</t>
+          <t>414130</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>303126</t>
+          <t>382752</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>411233</t>
+          <t>447048</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>601923</t>
+          <t>661222</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>512049</t>
+          <t>613456</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>659755</t>
+          <t>709193</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>524484</t>
+          <t>575635</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>417499</t>
+          <t>527246</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>583326</t>
+          <t>623218</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>668456</t>
+          <t>736231</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>528572</t>
+          <t>696332</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>724153</t>
+          <t>777027</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1192940</t>
+          <t>1311866</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1016948</t>
+          <t>1249186</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1291411</t>
+          <t>1370248</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2360000</t>
+          <t>2332199</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2263645</t>
+          <t>2271067</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2548960</t>
+          <t>2391268</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>67,79%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>69,51%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2185615</t>
+          <t>2091276</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2078900</t>
+          <t>2038298</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2507773</t>
+          <t>2140731</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>56,08%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>4545615</t>
+          <t>4423476</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4374850</t>
+          <t>4349035</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>4923105</t>
+          <t>4501123</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>63,62%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3374062</t>
+          <t>3440406</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3374062</t>
+          <t>3440406</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3374062</t>
+          <t>3440406</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3575418</t>
+          <t>3634670</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6949480</t>
+          <t>7075077</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6949480</t>
+          <t>7075077</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6949480</t>
+          <t>7075077</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
